--- a/Source/BCIO-source-hierarchy.xlsx
+++ b/Source/BCIO-source-hierarchy.xlsx
@@ -445,14 +445,14 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>Cross reference</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Informal definition</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Cross reference</t>
-        </is>
-      </c>
       <c r="M1" t="inlineStr">
         <is>
           <t>Examples</t>
@@ -460,12 +460,12 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>Synonyms</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>Comment</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Synonyms</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:010126</t>
+          <t>BCIO:010106</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>amount of experience</t>
+          <t>number of people delivering intervention to each participant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -643,29 +643,24 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
+          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>full-day, 6 years</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:010106</t>
+          <t>BCIO:010126</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>number of people delivering intervention to each participant</t>
+          <t>amount of experience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -676,12 +671,17 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
+          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>full-day, 6 years</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OBI:0000245</t>
+          <t>BCIO:010108</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -732,7 +732,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
+          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -744,13 +744,13 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:010139</t>
+          <t>BCIO:010109</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>organisation source</t>
+          <t>age of person source</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -760,7 +760,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
+          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -772,15 +772,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:010123</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>expertise discipline</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>BCIO:010118</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>target behaviour of person source</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -788,7 +788,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>An attribute that is a field of knowledge or practice.</t>
+          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -798,25 +798,20 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
+          <t>source is highly physically active</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:010093</t>
+          <t>BCIO:010119</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>discipline of current programme of study or training</t>
+          <t>psychological influence on intervention delivery of person source</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -826,30 +821,25 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
+          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>psychology, medicine, hairdressing</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:010124</t>
+          <t>BCIO:010117</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>discipline of pre-existing knowledge or skill</t>
+          <t>health status of person source</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -859,7 +849,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
+          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -869,22 +859,22 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+          <t>diabetes, cancer, depression, obesity, overweight</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:010108</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>socio demographic attribute of person source</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>BCIO:010110</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>gender of person source</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -892,35 +882,40 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
+          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gender</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:010117</t>
+          <t>BCIO:010113</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>health status of person source</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>other gender</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
+          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -930,7 +925,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>diabetes, cancer, depression, obesity, overweight</t>
+          <t>non-binary, transexual</t>
         </is>
       </c>
     </row>
@@ -970,13 +965,13 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:010116</t>
+          <t>BCIO:010114</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>language proficiency of person source</t>
+          <t>ethnic group membership of person source</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -986,7 +981,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
+          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -996,20 +991,20 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>fluent, native</t>
+          <t>black, white, Indian, Chinese, Somalian</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:010109</t>
+          <t>BCIO:010116</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>age of person source</t>
+          <t>language proficiency of person source</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1019,27 +1014,32 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
+          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>fluent, native</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:010114</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ethnic group membership of person source</t>
-        </is>
-      </c>
+          <t>BCIO:010123</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>expertise discipline</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -1047,7 +1047,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
+          <t>An attribute that is a field of knowledge or practice.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1057,20 +1057,25 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>black, white, Indian, Chinese, Somalian</t>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:010118</t>
+          <t>BCIO:010124</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>target behaviour of person source</t>
+          <t>discipline of pre-existing knowledge or skill</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1080,7 +1085,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
+          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1090,20 +1095,20 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>source is highly physically active</t>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:010119</t>
+          <t>BCIO:010093</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>psychological influence on intervention delivery of person source</t>
+          <t>discipline of current programme of study or training</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1113,27 +1118,32 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
+          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>psychology, medicine, hairdressing</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:010110</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>gender of person source</t>
-        </is>
-      </c>
+          <t>MF:0000016</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -1141,40 +1151,35 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
+          <t>An extended organism that is a member of the species Homo sapiens.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gender</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:010113</t>
+          <t>BCIO:050842</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>other gender</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>role model for a person</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
+          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1182,24 +1187,24 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>non-binary, transexual</t>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:010003</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>personal role of source</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>BCIO:010095</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
@@ -1207,7 +1212,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>A role that inheres in a person source.</t>
+          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1219,23 +1224,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:010004</t>
+          <t>BCIO:010098</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>occupational role of source</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>sibling relationship</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
+          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1245,21 +1250,21 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Interventionist, facilitator, study staff</t>
+          <t>brother, sister, step-brother, step-sister</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:010077</t>
+          <t>BCIO:010099</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>skilled agricultural, forestry and fishery worker</t>
+          <t>child relationship</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1268,7 +1273,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
+          <t>A family member that is an offspring relationship from a person to their parent.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1278,21 +1283,21 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
+          <t>daughter, son, step-daughter, step-son</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:010006</t>
+          <t>BCIO:010097</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t>spouse or partner</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1301,195 +1306,185 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
+          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:010034</t>
+          <t>BCIO:010096</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>legal, social and cultural professional</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>parent or guardian</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
+          <t>A family member that is a mother, father or legal carer of a child.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>mother, father, step-mother, step-father, guardian</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:010043</t>
+          <t>BCIO:010002</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>creative and performing artist</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
+          <t>A person who is the bearer of a behaviour change intervention source role.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:010036</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>OBI:0000245</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>organization</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>librarian, archivist and curator</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
+          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Librarian, Archivist,  Curator</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:010041</t>
+          <t>BCIO:010139</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>organisation source</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>author and journalist</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
+          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Author, Writer, Journalist, Translator, News anchor</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:010042</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>BCIO:015098</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>gender identity</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>linguist</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
+          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Interpretator; other linguist</t>
+          <t>Population</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:010035</t>
+          <t>BCIO:010112</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>male gender</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>legal professional</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
+          <t>A gender identity as being male.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1499,30 +1494,30 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Lawyer, Judge, Coroner</t>
+          <t>male, man</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:010037</t>
+          <t>BCIO:010111</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>female gender</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>social professional</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
+          <t>A gender identity as being female.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1532,30 +1527,30 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
+          <t>female, woman</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:010038</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>BCIO:010129</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>volunteering of person source</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>psychologist</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
+          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1565,63 +1560,58 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
+          <t>voluntary basis, volunteering</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:010039</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>BCIO:010130</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>payment of person source</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>social work and counselling professional</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
+          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:010040</t>
+          <t>BCIO:010131</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>monetary payment</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>religious professional</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
+          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1631,30 +1621,30 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
+          <t>paid in cash, vouchers</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:010025</t>
+          <t>BCIO:010132</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>non-monetary payment</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>teaching professional</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
+          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -1664,30 +1654,30 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
+          <t>course credit</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:010032</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>BCIO:010128</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>supervision of person source</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>music teacher</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
+          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -1697,162 +1687,142 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
+          <t>supervised</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:010028</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>BCIO:010000</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>secondary education teacher</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
+          <t>A role played by a person, population or organisation that provides a BCI.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Secondary school teacher, High school teacher</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:010031</t>
+          <t>BCIO:010134</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>source involved in development of intervention</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>special needs teacher</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
+          <t>A BCI source that is involved in the development of intervention content.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:010030</t>
+          <t>BCIO:010135</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>source involved in co-production of intervention</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>early childhood educator</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
+          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Early childhood educator, Pre-school teacher</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:010033</t>
+          <t>BCIO:010138</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>organisational source role</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>arts teacher</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
+          <t>A BCI source role that is borne by an organisation.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:010029</t>
+          <t>BCIO:010133</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>source role related to intervention</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>primary school teacher</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
+          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -1864,150 +1834,140 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:010027</t>
+          <t>BCIO:010001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>person source role</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>vocational education teacher</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
+          <t>A behaviour change intervention source role that inheres in a person.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:010026</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>BCIO:010084</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>university and higher education teacher</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
+          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:010007</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>vocational training student or trainee</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>science and engineering professional</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
+          <t>A student or trainee that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:010044</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>higher education student or trainee</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>technician and associate professional</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
+          <t>A student or trainee that is currently learning on an advanced educational programme in a university, college or professional school.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:010059</t>
+          <t>BCIO:010092</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>doctoral student or trainee</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>social work associate professional</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
+          <t>A higher education student or trainee that is currently studying for a doctoral degree.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2017,30 +1977,30 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
+          <t>PhD student</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:010057</t>
+          <t>BCIO:010090</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>graduate student or trainee</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>business and administration associate professional</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
+          <t>A higher education student or trainee that has completed an undergraduate degree.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2050,30 +2010,30 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
+          <t>graduate student</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:010058</t>
+          <t>BCIO:010091</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>masters student or trainee</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>legal and related associate professional</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
+          <t>A higher education student or trainee that is currently studying for a Masters degree.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2083,30 +2043,30 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
+          <t>MSc student, Masters student</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:010045</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>undergraduate student or trainee</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>health associate professional</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
+          <t>A higher education student or trainee that is currently studying for an undergraduate degree.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2116,327 +2076,282 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Veterinary Technician </t>
+          <t>undergraduate student</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:010050</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>school student or trainee</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>traditional and complementary medicine associate professional</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
+          <t>A student or trainee that is currently learning at a primary or secondary education level in an institutional, organised setting.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:010053</t>
+          <t>BCIO:010085</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>informal education student or trainee</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>physiotherapy technician and assistant</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
+          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:010047</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>BCIO:010003</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>personal role of source</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>nursing and midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
+          <t>A role that inheres in a person source.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:010048</t>
+          <t>BCIO:010094</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>relatedness between person source and the target population</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>nursing associate professional</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
+          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:010049</t>
+          <t>BCIO:010102</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>colleague</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
+          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Assistant midwife, Traditional midwife</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:010054</t>
+          <t>BCIO:010101</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>medical assistant</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
+          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:010046</t>
+          <t>BCIO:010105</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>embedded in participants’ community</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>medical and pharmaceutical technician</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
+          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:010056</t>
+          <t>BCIO:010104</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>peer</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>ambulance worker</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
+          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:010052</t>
+          <t>BCIO:010103</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>employer</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>community health worker</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
+          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:010051</t>
+          <t>BCIO:010100</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>carer</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>dental assistant and therapist</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
+          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -2446,31 +2361,30 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Dental assistant, Dental hygienist , Dental therapist</t>
+          <t>carer</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:010055</t>
+          <t>BCIO:010004</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>occupational role of source</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>environmental and occupational health inspector and associate</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
-workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
+          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -2480,63 +2394,58 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
+          <t>Interventionist, facilitator, study staff</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:010065</t>
+          <t>BCIO:010006</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>professional</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>artistic, cultural and culinary associate professional</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
+          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:010066</t>
+          <t>BCIO:010008</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>information and communications technician</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>health professional</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
+          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2546,14 +2455,14 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
+          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:010061</t>
+          <t>BCIO:010015</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2562,14 +2471,14 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>sport and fitness worker</t>
+          <t>traditional and complementary medicine professional</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
+          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2579,63 +2488,58 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
+          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:010063</t>
+          <t>BCIO:010012</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>sports coach, instructor and official</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>nursing and midwifery professional</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
+          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:010062</t>
+          <t>BCIO:010016</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>athlete and sports player</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>paramedical practitioner</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
+          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2645,30 +2549,30 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
+          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:010064</t>
+          <t>BCIO:010019</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>fitness and recreation instructor and programme leader</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>pharmacist</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
+          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2678,14 +2582,14 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
+          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:010060</t>
+          <t>BCIO:010017</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2694,14 +2598,14 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>religious associate professional</t>
+          <t>veterinarian</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
+          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2711,30 +2615,30 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Faith healer, Lay preacher, Monk, Nun</t>
+          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:010008</t>
+          <t>BCIO:010014</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>health professional</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>midwifery professional</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
+          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2744,14 +2648,14 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
+          <t>Midwife</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:010014</t>
+          <t>BCIO:010009</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2760,14 +2664,14 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>midwifery professional</t>
+          <t>medical doctor</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
+          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -2777,30 +2681,30 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:010019</t>
+          <t>BCIO:010010</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>pharmacist</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>generalist medical practitioner</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -2810,30 +2714,30 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
+          <t>Primary care physician, family doctor, GP</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:010017</t>
+          <t>BCIO:010011</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>veterinarian</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>specialist medical practitioner</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -2843,14 +2747,14 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
+          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:010023</t>
+          <t>BCIO:010013</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2859,14 +2763,14 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>audiologist and speech therapist</t>
+          <t>nursing professional</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
+          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -2876,14 +2780,14 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
+          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:010012</t>
+          <t>BCIO:010023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2892,26 +2796,31 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>nursing and midwifery professional</t>
+          <t>audiologist and speech therapist</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
+          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:010024</t>
+          <t>BCIO:010021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -2920,14 +2829,14 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>optometrist and ophthalmic optician</t>
+          <t>physiotherapist</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
+          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -2937,14 +2846,14 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
+          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:010013</t>
+          <t>BCIO:010020</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -2953,14 +2862,14 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>nursing professional</t>
+          <t>environmental and occupational health and hygiene professional</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
+          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -2970,14 +2879,14 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
+          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:010016</t>
+          <t>BCIO:010022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2986,14 +2895,14 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>paramedical practitioner</t>
+          <t>dietician and nutritionist</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
+          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3003,14 +2912,14 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
+          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:010022</t>
+          <t>BCIO:010018</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3019,14 +2928,14 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>dietician and nutritionist</t>
+          <t>dentist</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
+          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3036,14 +2945,14 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
+          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:010009</t>
+          <t>BCIO:010024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3052,14 +2961,14 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>medical doctor</t>
+          <t>optometrist and ophthalmic optician</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
+          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3069,63 +2978,58 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
+          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:010010</t>
+          <t>BCIO:010044</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>technician and associate professional</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>generalist medical practitioner</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
+          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Primary care physician, family doctor, GP</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:010011</t>
+          <t>BCIO:010061</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>specialist medical practitioner</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>sport and fitness worker</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
+          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3135,30 +3039,30 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
+          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:010015</t>
+          <t>BCIO:010063</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>traditional and complementary medicine professional</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>sports coach, instructor and official</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
+          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3168,30 +3072,30 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
+          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:010020</t>
+          <t>BCIO:010064</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>environmental and occupational health and hygiene professional</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>fitness and recreation instructor and programme leader</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
+          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3201,30 +3105,30 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
+          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:010018</t>
+          <t>BCIO:010062</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>dentist</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>athlete and sports player</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
+          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3234,14 +3138,14 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
+          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:010021</t>
+          <t>BCIO:010058</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3250,14 +3154,14 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>physiotherapist</t>
+          <t>legal and related associate professional</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
+          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3267,30 +3171,30 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
+          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:010082</t>
+          <t>BCIO:010060</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>armed forces occupation</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>religious associate professional</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
+          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3300,30 +3204,30 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
+          <t>Faith healer, Lay preacher, Monk, Nun</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:010078</t>
+          <t>BCIO:010066</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>craft and related trades worker</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>information and communications technician</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
+          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3333,30 +3237,30 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
+          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:010083</t>
+          <t>BCIO:010057</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>researcher</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>business and administration associate professional</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>An occupational role that is a researcher but unclear what discipline.</t>
+          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3366,30 +3270,30 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>researcher, research assistant, investigator</t>
+          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:010067</t>
+          <t>BCIO:010045</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>clerical support worker</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>health associate professional</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
+          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3399,30 +3303,30 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
+          <t xml:space="preserve">Veterinary Technician </t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:010081</t>
+          <t>BCIO:010051</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>elementary occupation</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>dental assistant and therapist</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
+          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -3432,30 +3336,30 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
+          <t>Dental assistant, Dental hygienist , Dental therapist</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:010005</t>
+          <t>BCIO:010053</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>manager</t>
-        </is>
-      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>physiotherapy technician and assistant</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
+          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -3465,30 +3369,30 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
+          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:010079</t>
+          <t>BCIO:010056</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>plant and machine operator</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ambulance worker</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
+          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -3498,86 +3402,96 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
+          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:010080</t>
+          <t>BCIO:010050</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>assembler</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>traditional and complementary medicine associate professional</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
+          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:010068</t>
+          <t>BCIO:010052</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>services and sales worker</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>community health worker</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
+          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:010070</t>
+          <t>BCIO:010046</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>sales worker</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>medical and pharmaceutical technician</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
+          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -3587,30 +3501,30 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
+          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:010076</t>
+          <t>BCIO:010047</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>protective services worker</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>nursing and midwifery associate professional</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
+          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -3620,30 +3534,30 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
+          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:010071</t>
+          <t>BCIO:010048</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>personal care worker</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>nursing associate professional</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
+          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -3653,30 +3567,30 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Personal carer</t>
+          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:010073</t>
+          <t>BCIO:010049</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>teachers’ aide</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>midwifery associate professional</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
+          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -3686,30 +3600,30 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Pre-school assistant, Teacher’s assistant</t>
+          <t>Assistant midwife, Traditional midwife</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:010074</t>
+          <t>BCIO:010054</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>health care assistant</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>medical assistant</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
+          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -3719,30 +3633,31 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
+          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:010075</t>
+          <t>BCIO:010055</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>home-based personal care worker</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>environmental and occupational health inspector and associate</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
+          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
+workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -3752,14 +3667,14 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
+          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:010072</t>
+          <t>BCIO:010065</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -3768,14 +3683,14 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>child care worker</t>
+          <t>artistic, cultural and culinary associate professional</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
+          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -3785,30 +3700,30 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
+          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:010069</t>
+          <t>BCIO:010059</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>personal services worker</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>social work associate professional</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
+          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -3818,58 +3733,63 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
+          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:010094</t>
+          <t>BCIO:010025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>relatedness between person source and the target population</t>
-        </is>
-      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>teaching professional</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
+          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:010102</t>
+          <t>BCIO:010029</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>colleague</t>
-        </is>
-      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>primary school teacher</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
+          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -3881,135 +3801,155 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:010103</t>
+          <t>BCIO:010033</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>employer</t>
-        </is>
-      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>arts teacher</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
+          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:010105</t>
+          <t>BCIO:010031</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>embedded in participants’ community</t>
-        </is>
-      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>special needs teacher</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
+          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:010101</t>
+          <t>BCIO:010032</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>friend</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>music teacher</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
+          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:010104</t>
+          <t>BCIO:010027</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>peer</t>
-        </is>
-      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>vocational education teacher</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
+          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:010100</t>
+          <t>BCIO:010026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>carer</t>
-        </is>
-      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>university and higher education teacher</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
+          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -4019,86 +3959,96 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>carer</t>
+          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:010000</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>behaviour change intervention source</t>
-        </is>
-      </c>
+          <t>BCIO:010030</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>early childhood educator</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>A role played by a person, population or organisation that provides a BCI.</t>
+          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Early childhood educator, Pre-school teacher</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:010134</t>
+          <t>BCIO:010028</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>source involved in development of intervention</t>
-        </is>
-      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>secondary education teacher</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>A BCI source that is involved in the development of intervention content.</t>
+          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Secondary school teacher, High school teacher</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:010135</t>
+          <t>BCIO:010034</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>source involved in co-production of intervention</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>legal, social and cultural professional</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -4110,219 +4060,254 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:010138</t>
+          <t>BCIO:010043</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>organisational source role</t>
-        </is>
-      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>creative and performing artist</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>A BCI source role that is borne by an organisation.</t>
+          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:010133</t>
+          <t>BCIO:010040</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>source role related to intervention</t>
-        </is>
-      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>religious professional</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
+          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:010001</t>
+          <t>BCIO:010036</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>person source role</t>
-        </is>
-      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>librarian, archivist and curator</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>A behaviour change intervention source role that inheres in a person.</t>
+          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Librarian, Archivist,  Curator</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+          <t>BCIO:010042</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>linguist</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Interpretator; other linguist</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>BCIO:010035</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>school student or trainee</t>
-        </is>
-      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>legal professional</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Lawyer, Judge, Coroner</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
+          <t>BCIO:010041</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>informal education student or trainee</t>
-        </is>
-      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>author and journalist</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
+          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Author, Writer, Journalist, Translator, News anchor</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:010037</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee</t>
-        </is>
-      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>social professional</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
+          <t>BCIO:010039</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>higher education student or trainee</t>
-        </is>
-      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>social work and counselling professional</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning on an advanced educational programme in a university, college or professional school.</t>
+          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -4332,30 +4317,30 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>BCIO:010038</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>masters student or trainee</t>
-        </is>
-      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>psychologist</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for a Masters degree.</t>
+          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -4365,30 +4350,30 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>MSc student, Masters student</t>
+          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:010007</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>undergraduate student or trainee</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>science and engineering professional</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for an undergraduate degree.</t>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -4398,21 +4383,21 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>undergraduate student</t>
+          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
+          <t>BCIO:010081</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>doctoral student or trainee</t>
+          <t>elementary occupation</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -4421,7 +4406,7 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for a doctoral degree.</t>
+          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -4431,21 +4416,21 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>PhD student</t>
+          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
+          <t>BCIO:010080</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>graduate student or trainee</t>
+          <t>assembler</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -4454,115 +4439,125 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that has completed an undergraduate degree.</t>
+          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>graduate student</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MF:0000016</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+          <t>BCIO:010078</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>craft and related trades worker</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>An extended organism that is a member of the species Homo sapiens.</t>
+          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:010002</t>
+          <t>BCIO:010005</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>A person who is the bearer of a behaviour change intervention source role.</t>
+          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:010095</t>
+          <t>BCIO:010067</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>clerical support worker</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
+          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:010096</t>
+          <t>BCIO:010083</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>parent or guardian</t>
+          <t>researcher</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -4571,7 +4566,7 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>A family member that is a mother, father or legal carer of a child.</t>
+          <t>An occupational role that is a researcher but unclear what discipline.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -4581,21 +4576,21 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>mother, father, step-mother, step-father, guardian</t>
+          <t>researcher, research assistant, investigator</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:010097</t>
+          <t>BCIO:010079</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>spouse or partner</t>
+          <t>plant and machine operator</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -4604,7 +4599,7 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
+          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -4614,21 +4609,21 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
+          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:010098</t>
+          <t>BCIO:010082</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>sibling relationship</t>
+          <t>armed forces occupation</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -4637,7 +4632,7 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
+          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -4647,21 +4642,21 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>brother, sister, step-brother, step-sister</t>
+          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:010099</t>
+          <t>BCIO:010077</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>child relationship</t>
+          <t>skilled agricultural, forestry and fishery worker</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -4670,7 +4665,7 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>A family member that is an offspring relationship from a person to their parent.</t>
+          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -4680,91 +4675,91 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>daughter, son, step-daughter, step-son</t>
+          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:050842</t>
+          <t>BCIO:010068</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>role model for a person</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>services and sales worker</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
+          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:015098</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>gender identity</t>
-        </is>
-      </c>
+          <t>BCIO:010076</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>protective services worker</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
+          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:010112</t>
+          <t>BCIO:010071</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>male gender</t>
-        </is>
-      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>personal care worker</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>A gender identity as being male.</t>
+          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -4774,30 +4769,30 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>male, man</t>
+          <t>Personal carer</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:010111</t>
+          <t>BCIO:010074</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>female gender</t>
-        </is>
-      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>health care assistant</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>A gender identity as being female.</t>
+          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -4807,30 +4802,30 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>female, woman</t>
+          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BCIO:010129</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>volunteering of person source</t>
-        </is>
-      </c>
+          <t>BCIO:010072</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>child care worker</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
+          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -4840,58 +4835,63 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>voluntary basis, volunteering</t>
+          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:010130</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>payment of person source</t>
-        </is>
-      </c>
+          <t>BCIO:010075</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>home-based personal care worker</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
+          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:010131</t>
+          <t>BCIO:010073</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>monetary payment</t>
-        </is>
-      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>teachers’ aide</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
+          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -4901,30 +4901,30 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>paid in cash, vouchers</t>
+          <t>Pre-school assistant, Teacher’s assistant</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:010132</t>
+          <t>BCIO:010069</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>non-monetary payment</t>
-        </is>
-      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>personal services worker</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
+          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -4934,30 +4934,30 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>course credit</t>
+          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:010128</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>supervision of person source</t>
-        </is>
-      </c>
+          <t>BCIO:010070</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>sales worker</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
+          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>supervised</t>
+          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
         </is>
       </c>
     </row>

--- a/Source/BCIO-source-hierarchy.xlsx
+++ b/Source/BCIO-source-hierarchy.xlsx
@@ -1260,7 +1260,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>dose range specification</t>
+          <t>spécification d’intervalle de dose</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1272,7 +1272,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>An information content entity that specifies the minimum and maximum quantities of drug product or active ingredient in a dose administration.</t>
+          <t>Une entité de contenu informationnel qui spécifie les quantités minimum et maximum de médicament ou d’ingrédient actif dans une administration de dose.</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>A continuant that inheres in or is borne by other entities. Every instance of A requires some specific instance of B which must always be the same.</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">A mental disposition is a bodily disposition that is realized in a mental process. </t>
+          <t>A &lt;bodily disposition&gt; that is realized in a mental process.</t>
         </is>
       </c>
     </row>
@@ -7215,7 +7215,7 @@
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>fiat object part</t>
+          <t>fiat object</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -8298,7 +8298,7 @@
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr">
         <is>
-          <t>établissement de pharmacologie</t>
+          <t>pharmacy facility</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -8403,7 +8403,7 @@
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>organisation</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -9344,7 +9344,7 @@
       <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organism participates.</t>
+          <t>A process in which at least one bodily component of an organsim participates.</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr">
         <is>
-          <t>A mental process that has positive or negative valence.</t>
+          <t>A &lt;mental process&gt; that has positive or negative valence.</t>
         </is>
       </c>
     </row>
